--- a/Questions Bulk Creation Template.xlsx
+++ b/Questions Bulk Creation Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed Aiman\Desktop\Quick Stop Solution LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83034B66-DF59-4D48-A7C2-DBAF37B684FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F81A51F-FB4B-4EEC-BCDF-212C95D24338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{37E97DEB-405A-467F-9D2A-E3DA61B5D00F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">Question </t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Option D</t>
+  </si>
+  <si>
+    <t>Device Model</t>
   </si>
 </sst>
 </file>
@@ -431,13 +434,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47D46DA-37BF-4912-82F5-30D9FF87F660}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="23.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,21 +449,24 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Questions Bulk Creation Template.xlsx
+++ b/Questions Bulk Creation Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed Aiman\Desktop\Quick Stop Solution LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F81A51F-FB4B-4EEC-BCDF-212C95D24338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B92752-9934-4EAE-85E8-AD8C21D87DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{37E97DEB-405A-467F-9D2A-E3DA61B5D00F}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <t>Option D</t>
   </si>
   <si>
-    <t>Device Model</t>
+    <t>Module</t>
   </si>
 </sst>
 </file>
